--- a/Requisitos No Funcionales.xlsx
+++ b/Requisitos No Funcionales.xlsx
@@ -1,17 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucia\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId5"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="44">
   <si>
     <t>Identificador (ID) de la historia</t>
   </si>
@@ -131,37 +139,63 @@
   </si>
   <si>
     <t>Entregables académ</t>
+  </si>
+  <si>
+    <t>RNF-10</t>
+  </si>
+  <si>
+    <t>Tiempo de actividad (Uptime)</t>
+  </si>
+  <si>
+    <t>El sistema debe garantizar un nivel de disponibilidad de al menos el 99,5% de lunes a sábado, en la ventana horaria comprendida entre las 12:00 y las 16:00 horas (horario peak de alta demanda de pedidos).</t>
+  </si>
+  <si>
+    <t>Disponibilidad software</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -183,32 +217,46 @@
     </fill>
   </fills>
   <borders count="8">
-    <border/>
     <border>
       <left/>
+      <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -218,6 +266,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -232,6 +281,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -243,6 +293,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -251,49 +303,59 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -301,7 +363,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -491,420 +553,432 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.38"/>
-    <col customWidth="1" min="2" max="2" width="18.25"/>
-    <col customWidth="1" min="3" max="3" width="20.75"/>
-    <col customWidth="1" min="4" max="4" width="40.0"/>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.77734375" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="9"/>
+    </row>
+    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="7" t="s">
+    <row r="3" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="84.75" customHeight="1">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="6">
+    <row r="4" spans="1:4" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+    </row>
+    <row r="6" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+    <row r="8" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" ht="61.5" customHeight="1">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-    </row>
-    <row r="11">
+    <row r="9" spans="1:4" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="11" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
+    <row r="13" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="67.5" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="16">
+    <row r="14" spans="1:4" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="16" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="9"/>
+    </row>
+    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" ht="66.75" customHeight="1">
-      <c r="A19" s="9"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="21">
+    <row r="19" spans="1:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="21" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
+      <c r="B21" s="7"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+    </row>
+    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="s">
+    <row r="23" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" ht="62.25" customHeight="1">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-    </row>
-    <row r="26">
+    <row r="24" spans="1:4" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+    </row>
+    <row r="26" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+      <c r="B26" s="7"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="s">
+    <row r="28" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="8" t="s">
+      <c r="D28" s="6" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" ht="70.5" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-    </row>
-    <row r="31">
+    <row r="29" spans="1:4" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+    </row>
+    <row r="31" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+    </row>
+    <row r="32" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" ht="64.5" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-    </row>
-    <row r="36">
+    <row r="34" spans="1:4" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+    </row>
+    <row r="36" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="s">
+      <c r="B36" s="7"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="9"/>
+    </row>
+    <row r="37" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" ht="68.25" customHeight="1">
-      <c r="A39" s="9"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-    </row>
-    <row r="41">
+    <row r="39" spans="1:4" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+    </row>
+    <row r="41" spans="1:4" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="s">
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="9"/>
+    </row>
+    <row r="42" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="7" t="s">
+    <row r="43" spans="1:4" ht="13.2" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="44" ht="60.0" customHeight="1">
-      <c r="A44" s="9"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
+    <row r="44" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="9"/>
+    </row>
+    <row r="47" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="73.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:D39"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B41:D41"/>
+  <mergeCells count="50">
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B33:B34"/>
     <mergeCell ref="B31:D31"/>
@@ -914,7 +988,44 @@
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="A38:A39"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="B1:D1"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>